--- a/data/wireless-technologies/antennas-and-adapters.xlsx
+++ b/data/wireless-technologies/antennas-and-adapters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\react\dielcom\dielcom\data\wireless-technologies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A46730-460F-4E9A-A0DE-72BCD65A6FC0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E783F4FA-D293-49D8-A7EF-AA8866785329}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -1192,7 +1192,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Y991"/>
+  <dimension ref="A1:Y990"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" customWidth="1"/>
@@ -1243,19 +1243,23 @@
       <c r="Y1" s="3"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
+      <c r="A2" s="6" t="s">
+        <v>240</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
+        <v>13</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="F2" s="7" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -1285,13 +1289,15 @@
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="F3" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
@@ -1320,7 +1326,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>6</v>
@@ -1357,14 +1363,16 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="7"/>
+      <c r="E5" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="F5" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -1394,17 +1402,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>12</v>
-      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -1433,16 +1437,16 @@
         <v>1</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -1472,7 +1476,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>6</v>
@@ -1511,16 +1515,14 @@
         <v>1</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>11</v>
-      </c>
+      <c r="E9" s="7"/>
       <c r="F9" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -1550,14 +1552,14 @@
         <v>1</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
@@ -1587,14 +1589,16 @@
         <v>1</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="7"/>
+      <c r="E11" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="F11" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -1624,16 +1628,16 @@
         <v>1</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
@@ -1663,17 +1667,15 @@
         <v>1</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="E13" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="7"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -1702,15 +1704,17 @@
         <v>1</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E14" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="7"/>
+      <c r="E14" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -1733,22 +1737,22 @@
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
@@ -1772,22 +1776,20 @@
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>31</v>
-      </c>
+      <c r="E16" s="7"/>
       <c r="F16" s="7" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
@@ -1817,7 +1819,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>6</v>
@@ -1854,7 +1856,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>6</v>
@@ -1885,20 +1887,22 @@
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>242</v>
+        <v>5</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E19" s="7"/>
+      <c r="E19" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="F19" s="7" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
@@ -1922,22 +1926,20 @@
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>5</v>
+        <v>243</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>37</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="E20" s="7"/>
       <c r="F20" s="7" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
@@ -1961,20 +1963,20 @@
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>243</v>
+        <v>274</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E21" s="7"/>
-      <c r="F21" s="7" t="s">
-        <v>40</v>
+      <c r="F21" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
@@ -2004,7 +2006,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>42</v>
@@ -2041,14 +2043,16 @@
         <v>1</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="7"/>
-      <c r="F23" s="4" t="s">
-        <v>43</v>
+      <c r="E23" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
@@ -2078,16 +2082,14 @@
         <v>1</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>47</v>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -2117,14 +2119,16 @@
         <v>1</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="7"/>
+      <c r="E25" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="F25" s="7" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
@@ -2148,23 +2152,19 @@
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>274</v>
+        <v>244</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>12</v>
-      </c>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
@@ -2187,19 +2187,21 @@
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
+      <c r="F27" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
@@ -2222,13 +2224,13 @@
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>273</v>
+        <v>245</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>52</v>
@@ -2265,15 +2267,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>52</v>
       </c>
       <c r="E29" s="7"/>
-      <c r="F29" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="F29" s="7"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
@@ -2302,7 +2302,7 @@
         <v>1</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>52</v>
@@ -2331,19 +2331,23 @@
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
+        <v>57</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
@@ -2366,22 +2370,18 @@
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>275</v>
+        <v>73</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>11</v>
-      </c>
+      <c r="C32" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
       <c r="F32" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
@@ -2411,12 +2411,12 @@
         <v>1</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
@@ -2439,19 +2439,19 @@
       <c r="Y33" s="3"/>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="7" t="s">
         <v>73</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
@@ -2474,14 +2474,14 @@
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="6" t="s">
         <v>73</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
@@ -2516,7 +2516,7 @@
         <v>1</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
@@ -2551,7 +2551,7 @@
         <v>1</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
@@ -2586,7 +2586,7 @@
         <v>1</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
@@ -2621,7 +2621,7 @@
         <v>1</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
@@ -2656,12 +2656,12 @@
         <v>1</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
-      <c r="F40" s="7" t="s">
-        <v>60</v>
+      <c r="F40" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -2691,12 +2691,12 @@
         <v>1</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
       <c r="F41" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
@@ -2726,12 +2726,12 @@
         <v>1</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
       <c r="F42" s="8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
@@ -2761,12 +2761,12 @@
         <v>1</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
-      <c r="F43" s="8" t="s">
-        <v>74</v>
+      <c r="F43" s="7" t="s">
+        <v>60</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
@@ -2796,7 +2796,7 @@
         <v>1</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
@@ -2831,13 +2831,11 @@
         <v>1</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
-      <c r="F45" s="7" t="s">
-        <v>60</v>
-      </c>
+      <c r="F45" s="7"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
@@ -2860,17 +2858,19 @@
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>73</v>
+        <v>246</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
+      <c r="F46" s="7" t="s">
+        <v>71</v>
+      </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
@@ -2899,12 +2899,12 @@
         <v>1</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
@@ -2934,12 +2934,12 @@
         <v>1</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -2969,12 +2969,12 @@
         <v>1</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
@@ -2998,18 +2998,22 @@
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C50" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7" t="s">
-        <v>84</v>
+      <c r="C50" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
@@ -3039,13 +3043,13 @@
         <v>1</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>86</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>74</v>
@@ -3072,22 +3076,20 @@
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>247</v>
+        <v>90</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>74</v>
+        <v>89</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
@@ -3111,21 +3113,17 @@
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>90</v>
+        <v>248</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C53" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>91</v>
-      </c>
+      <c r="C53" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D53" s="7"/>
       <c r="E53" s="7"/>
-      <c r="F53" s="7" t="s">
-        <v>92</v>
-      </c>
+      <c r="F53" s="7"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
@@ -3148,16 +3146,20 @@
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C54" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
+      <c r="C54" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>96</v>
+      </c>
       <c r="F54" s="7"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
@@ -3181,20 +3183,18 @@
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>96</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E55" s="7"/>
       <c r="F55" s="7"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
@@ -3218,19 +3218,19 @@
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>250</v>
+        <v>99</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>98</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D56" s="7"/>
       <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
+      <c r="F56" s="7" t="s">
+        <v>101</v>
+      </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
@@ -3253,19 +3253,17 @@
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>99</v>
+        <v>251</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="6" t="s">
-        <v>100</v>
+      <c r="C57" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="D57" s="7"/>
       <c r="E57" s="7"/>
-      <c r="F57" s="7" t="s">
-        <v>101</v>
-      </c>
+      <c r="F57" s="7"/>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
@@ -3288,17 +3286,19 @@
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>251</v>
+        <v>104</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C58" s="7" t="s">
-        <v>102</v>
+      <c r="C58" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="D58" s="7"/>
       <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
+      <c r="F58" s="7" t="s">
+        <v>105</v>
+      </c>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
@@ -3321,18 +3321,20 @@
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>104</v>
+        <v>252</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D59" s="7"/>
+        <v>106</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>107</v>
+      </c>
       <c r="E59" s="7"/>
-      <c r="F59" s="7" t="s">
-        <v>105</v>
+      <c r="F59" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
@@ -3356,20 +3358,18 @@
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>252</v>
+        <v>109</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>107</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="D60" s="7"/>
       <c r="E60" s="7"/>
-      <c r="F60" s="8" t="s">
-        <v>74</v>
+      <c r="F60" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
@@ -3399,7 +3399,7 @@
         <v>1</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D61" s="7"/>
       <c r="E61" s="7"/>
@@ -3434,7 +3434,7 @@
         <v>1</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D62" s="7"/>
       <c r="E62" s="7"/>
@@ -3463,18 +3463,18 @@
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>109</v>
+        <v>253</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D63" s="7"/>
       <c r="E63" s="7"/>
-      <c r="F63" s="7" t="s">
-        <v>110</v>
+      <c r="F63" s="8" t="s">
+        <v>113</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
@@ -3498,18 +3498,20 @@
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="8" t="s">
-        <v>113</v>
+      <c r="E64" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>116</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
@@ -3533,20 +3535,18 @@
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D65" s="7"/>
-      <c r="E65" s="7" t="s">
-        <v>115</v>
-      </c>
+      <c r="E65" s="7"/>
       <c r="F65" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
@@ -3570,18 +3570,22 @@
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
+        <v>119</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>115</v>
+      </c>
       <c r="F66" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
@@ -3605,22 +3609,18 @@
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E67" s="7" t="s">
-        <v>115</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
       <c r="F67" s="7" t="s">
-        <v>121</v>
+        <v>19</v>
       </c>
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
@@ -3644,18 +3644,20 @@
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D68" s="7"/>
+        <v>100</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="E68" s="7"/>
-      <c r="F68" s="7" t="s">
-        <v>19</v>
+      <c r="F68" s="8" t="s">
+        <v>113</v>
       </c>
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
@@ -3679,20 +3681,22 @@
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C69" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="E69" s="7"/>
+      <c r="C69" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>126</v>
+      </c>
       <c r="F69" s="8" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="G69" s="3"/>
       <c r="H69" s="3"/>
@@ -3722,7 +3726,7 @@
         <v>1</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D70" s="7" t="s">
         <v>125</v>
@@ -3730,8 +3734,8 @@
       <c r="E70" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="F70" s="8" t="s">
-        <v>127</v>
+      <c r="F70" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
@@ -3761,7 +3765,7 @@
         <v>1</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D71" s="7" t="s">
         <v>125</v>
@@ -3770,7 +3774,7 @@
         <v>126</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="G71" s="3"/>
       <c r="H71" s="3"/>
@@ -3800,7 +3804,7 @@
         <v>1</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D72" s="7" t="s">
         <v>125</v>
@@ -3809,7 +3813,7 @@
         <v>126</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
@@ -3839,7 +3843,7 @@
         <v>1</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D73" s="7" t="s">
         <v>125</v>
@@ -3848,7 +3852,7 @@
         <v>126</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
@@ -3878,7 +3882,7 @@
         <v>1</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D74" s="7" t="s">
         <v>125</v>
@@ -3911,22 +3915,22 @@
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C75" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>125</v>
+      <c r="C75" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>136</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>126</v>
+        <v>11</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
@@ -3956,7 +3960,7 @@
         <v>1</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>136</v>
@@ -3965,7 +3969,7 @@
         <v>11</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
@@ -3995,7 +3999,7 @@
         <v>1</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>136</v>
@@ -4004,7 +4008,7 @@
         <v>11</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G77" s="3"/>
       <c r="H77" s="3"/>
@@ -4034,7 +4038,7 @@
         <v>1</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>136</v>
@@ -4073,7 +4077,7 @@
         <v>1</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>136</v>
@@ -4082,7 +4086,7 @@
         <v>11</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G79" s="3"/>
       <c r="H79" s="3"/>
@@ -4112,13 +4116,13 @@
         <v>1</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>136</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F80" s="7" t="s">
         <v>19</v>
@@ -4144,21 +4148,19 @@
       <c r="Y80" s="3"/>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A81" s="6" t="s">
+      <c r="A81" s="7" t="s">
         <v>260</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="E81" s="7" t="s">
-        <v>23</v>
-      </c>
+      <c r="E81" s="7"/>
       <c r="F81" s="7" t="s">
         <v>19</v>
       </c>
@@ -4190,7 +4192,7 @@
         <v>1</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>136</v>
@@ -4227,7 +4229,7 @@
         <v>1</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>136</v>
@@ -4264,7 +4266,7 @@
         <v>1</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>136</v>
@@ -4301,7 +4303,7 @@
         <v>1</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>136</v>
@@ -4338,7 +4340,7 @@
         <v>1</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D86" s="8" t="s">
         <v>136</v>
@@ -4368,14 +4370,14 @@
       <c r="Y86" s="3"/>
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A87" s="7" t="s">
+      <c r="A87" s="6" t="s">
         <v>260</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D87" s="8" t="s">
         <v>136</v>
@@ -4412,7 +4414,7 @@
         <v>1</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D88" s="8" t="s">
         <v>136</v>
@@ -4443,20 +4445,20 @@
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="E89" s="7"/>
       <c r="F89" s="7" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="G89" s="3"/>
       <c r="H89" s="3"/>
@@ -4486,7 +4488,7 @@
         <v>1</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>151</v>
@@ -4523,7 +4525,7 @@
         <v>1</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>151</v>
@@ -4560,7 +4562,7 @@
         <v>1</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D92" s="8" t="s">
         <v>151</v>
@@ -4591,20 +4593,20 @@
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E93" s="7"/>
       <c r="F93" s="7" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G93" s="3"/>
       <c r="H93" s="3"/>
@@ -4634,7 +4636,7 @@
         <v>1</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D94" s="8" t="s">
         <v>156</v>
@@ -4671,7 +4673,7 @@
         <v>1</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>156</v>
@@ -4708,7 +4710,7 @@
         <v>1</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>156</v>
@@ -4745,10 +4747,10 @@
         <v>1</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E97" s="7"/>
       <c r="F97" s="7" t="s">
@@ -4782,7 +4784,7 @@
         <v>1</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>151</v>
@@ -4819,14 +4821,14 @@
         <v>1</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="D99" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="E99" s="7"/>
+        <v>162</v>
+      </c>
+      <c r="D99" s="7"/>
+      <c r="E99" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="F99" s="7" t="s">
-        <v>19</v>
+        <v>164</v>
       </c>
       <c r="G99" s="3"/>
       <c r="H99" s="3"/>
@@ -4856,14 +4858,14 @@
         <v>1</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D100" s="7"/>
       <c r="E100" s="7" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G100" s="3"/>
       <c r="H100" s="3"/>
@@ -4887,20 +4889,20 @@
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>262</v>
+        <v>169</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="D101" s="7"/>
-      <c r="E101" s="7" t="s">
-        <v>166</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="E101" s="7"/>
       <c r="F101" s="7" t="s">
-        <v>167</v>
+        <v>19</v>
       </c>
       <c r="G101" s="3"/>
       <c r="H101" s="3"/>
@@ -4924,21 +4926,19 @@
     </row>
     <row r="102" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>156</v>
+        <v>91</v>
       </c>
       <c r="E102" s="7"/>
-      <c r="F102" s="7" t="s">
-        <v>19</v>
-      </c>
+      <c r="F102" s="7"/>
       <c r="G102" s="3"/>
       <c r="H102" s="3"/>
       <c r="I102" s="3"/>
@@ -4967,13 +4967,15 @@
         <v>1</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D103" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E103" s="7"/>
-      <c r="F103" s="7"/>
+      <c r="F103" s="7" t="s">
+        <v>130</v>
+      </c>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
       <c r="I103" s="3"/>
@@ -5009,7 +5011,7 @@
       </c>
       <c r="E104" s="7"/>
       <c r="F104" s="7" t="s">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -5033,16 +5035,16 @@
     </row>
     <row r="105" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
-        <v>171</v>
+        <v>135</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="E105" s="7"/>
       <c r="F105" s="7" t="s">
@@ -5070,20 +5072,22 @@
     </row>
     <row r="106" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>135</v>
+        <v>263</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="E106" s="7"/>
-      <c r="F106" s="7" t="s">
-        <v>19</v>
+        <v>175</v>
+      </c>
+      <c r="E106" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
@@ -5107,22 +5111,18 @@
     </row>
     <row r="107" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="D107" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="E107" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="F107" s="8" t="s">
-        <v>74</v>
+        <v>177</v>
+      </c>
+      <c r="D107" s="7"/>
+      <c r="E107" s="7"/>
+      <c r="F107" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
@@ -5146,19 +5146,21 @@
     </row>
     <row r="108" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="D108" s="7"/>
-      <c r="E108" s="7"/>
-      <c r="F108" s="7" t="s">
-        <v>58</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="D108" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E108" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="F108" s="7"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
       <c r="I108" s="3"/>
@@ -5181,20 +5183,18 @@
     </row>
     <row r="109" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="E109" s="8" t="s">
-        <v>163</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="E109" s="7"/>
       <c r="F109" s="7"/>
       <c r="G109" s="3"/>
       <c r="H109" s="3"/>
@@ -5217,14 +5217,14 @@
       <c r="Y109" s="3"/>
     </row>
     <row r="110" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A110" s="6" t="s">
+      <c r="A110" s="7" t="s">
         <v>266</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D110" s="8" t="s">
         <v>123</v>
@@ -5252,20 +5252,22 @@
       <c r="Y110" s="3"/>
     </row>
     <row r="111" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A111" s="7" t="s">
+      <c r="A111" s="6" t="s">
         <v>266</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D111" s="8" t="s">
         <v>123</v>
       </c>
       <c r="E111" s="7"/>
-      <c r="F111" s="7"/>
+      <c r="F111" s="7" t="s">
+        <v>183</v>
+      </c>
       <c r="G111" s="3"/>
       <c r="H111" s="3"/>
       <c r="I111" s="3"/>
@@ -5287,22 +5289,20 @@
       <c r="Y111" s="3"/>
     </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A112" s="6" t="s">
+      <c r="A112" s="7" t="s">
         <v>266</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D112" s="8" t="s">
         <v>123</v>
       </c>
       <c r="E112" s="7"/>
-      <c r="F112" s="7" t="s">
-        <v>183</v>
-      </c>
+      <c r="F112" s="7"/>
       <c r="G112" s="3"/>
       <c r="H112" s="3"/>
       <c r="I112" s="3"/>
@@ -5324,20 +5324,24 @@
       <c r="Y112" s="3"/>
     </row>
     <row r="113" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A113" s="7" t="s">
-        <v>266</v>
+      <c r="A113" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D113" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="E113" s="7"/>
-      <c r="F113" s="7"/>
+        <v>185</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>74</v>
+      </c>
       <c r="G113" s="3"/>
       <c r="H113" s="3"/>
       <c r="I113" s="3"/>
@@ -5366,13 +5370,13 @@
         <v>1</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="D114" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>74</v>
@@ -5399,22 +5403,20 @@
     </row>
     <row r="115" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A115" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="D115" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E115" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="F115" s="8" t="s">
-        <v>74</v>
+        <v>174</v>
+      </c>
+      <c r="D115" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="E115" s="7"/>
+      <c r="F115" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="G115" s="3"/>
       <c r="H115" s="3"/>
@@ -5438,20 +5440,18 @@
     </row>
     <row r="116" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
-        <v>268</v>
+        <v>191</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="D116" s="8" t="s">
-        <v>175</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="D116" s="7"/>
       <c r="E116" s="7"/>
-      <c r="F116" s="7" t="s">
-        <v>190</v>
+      <c r="F116" s="8" t="s">
+        <v>193</v>
       </c>
       <c r="G116" s="3"/>
       <c r="H116" s="3"/>
@@ -5481,12 +5481,12 @@
         <v>1</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D117" s="7"/>
       <c r="E117" s="7"/>
       <c r="F117" s="8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G117" s="3"/>
       <c r="H117" s="3"/>
@@ -5516,12 +5516,12 @@
         <v>1</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D118" s="7"/>
       <c r="E118" s="7"/>
-      <c r="F118" s="8" t="s">
-        <v>195</v>
+      <c r="F118" s="7" t="s">
+        <v>197</v>
       </c>
       <c r="G118" s="3"/>
       <c r="H118" s="3"/>
@@ -5545,18 +5545,18 @@
     </row>
     <row r="119" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A119" s="6" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D119" s="7"/>
       <c r="E119" s="7"/>
-      <c r="F119" s="7" t="s">
-        <v>197</v>
+      <c r="F119" s="8" t="s">
+        <v>200</v>
       </c>
       <c r="G119" s="3"/>
       <c r="H119" s="3"/>
@@ -5586,12 +5586,12 @@
         <v>1</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D120" s="7"/>
       <c r="E120" s="7"/>
-      <c r="F120" s="8" t="s">
-        <v>200</v>
+      <c r="F120" s="7" t="s">
+        <v>202</v>
       </c>
       <c r="G120" s="3"/>
       <c r="H120" s="3"/>
@@ -5615,19 +5615,17 @@
     </row>
     <row r="121" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A121" s="6" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D121" s="7"/>
       <c r="E121" s="7"/>
-      <c r="F121" s="7" t="s">
-        <v>202</v>
-      </c>
+      <c r="F121" s="7"/>
       <c r="G121" s="3"/>
       <c r="H121" s="3"/>
       <c r="I121" s="3"/>
@@ -5650,17 +5648,19 @@
     </row>
     <row r="122" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
-        <v>203</v>
+        <v>269</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D122" s="7"/>
       <c r="E122" s="7"/>
-      <c r="F122" s="7"/>
+      <c r="F122" s="8" t="s">
+        <v>127</v>
+      </c>
       <c r="G122" s="3"/>
       <c r="H122" s="3"/>
       <c r="I122" s="3"/>
@@ -5683,13 +5683,13 @@
     </row>
     <row r="123" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A123" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D123" s="7"/>
       <c r="E123" s="7"/>
@@ -5718,18 +5718,18 @@
     </row>
     <row r="124" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A124" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C124" s="6" t="s">
-        <v>206</v>
+      <c r="C124" s="7" t="s">
+        <v>207</v>
       </c>
       <c r="D124" s="7"/>
       <c r="E124" s="7"/>
-      <c r="F124" s="8" t="s">
-        <v>127</v>
+      <c r="F124" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="G124" s="3"/>
       <c r="H124" s="3"/>
@@ -5758,13 +5758,13 @@
       <c r="B125" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C125" s="7" t="s">
-        <v>207</v>
+      <c r="C125" s="6" t="s">
+        <v>209</v>
       </c>
       <c r="D125" s="7"/>
       <c r="E125" s="7"/>
-      <c r="F125" s="7" t="s">
-        <v>208</v>
+      <c r="F125" s="6" t="s">
+        <v>210</v>
       </c>
       <c r="G125" s="3"/>
       <c r="H125" s="3"/>
@@ -5794,12 +5794,12 @@
         <v>1</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D126" s="7"/>
       <c r="E126" s="7"/>
-      <c r="F126" s="6" t="s">
-        <v>210</v>
+      <c r="F126" s="7" t="s">
+        <v>105</v>
       </c>
       <c r="G126" s="3"/>
       <c r="H126" s="3"/>
@@ -5829,12 +5829,12 @@
         <v>1</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D127" s="7"/>
       <c r="E127" s="7"/>
       <c r="F127" s="7" t="s">
-        <v>105</v>
+        <v>213</v>
       </c>
       <c r="G127" s="3"/>
       <c r="H127" s="3"/>
@@ -5864,7 +5864,7 @@
         <v>1</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D128" s="7"/>
       <c r="E128" s="7"/>
@@ -5899,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D129" s="7"/>
       <c r="E129" s="7"/>
@@ -5934,12 +5934,12 @@
         <v>1</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D130" s="7"/>
       <c r="E130" s="7"/>
-      <c r="F130" s="7" t="s">
-        <v>213</v>
+      <c r="F130" s="6" t="s">
+        <v>210</v>
       </c>
       <c r="G130" s="3"/>
       <c r="H130" s="3"/>
@@ -5969,7 +5969,7 @@
         <v>1</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D131" s="7"/>
       <c r="E131" s="7"/>
@@ -6003,13 +6003,13 @@
       <c r="B132" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C132" s="6" t="s">
-        <v>217</v>
+      <c r="C132" s="7" t="s">
+        <v>218</v>
       </c>
       <c r="D132" s="7"/>
       <c r="E132" s="7"/>
-      <c r="F132" s="6" t="s">
-        <v>210</v>
+      <c r="F132" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="G132" s="3"/>
       <c r="H132" s="3"/>
@@ -6039,7 +6039,7 @@
         <v>1</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D133" s="7"/>
       <c r="E133" s="7"/>
@@ -6074,7 +6074,7 @@
         <v>1</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D134" s="7"/>
       <c r="E134" s="7"/>
@@ -6109,7 +6109,7 @@
         <v>1</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D135" s="7"/>
       <c r="E135" s="7"/>
@@ -6144,7 +6144,7 @@
         <v>1</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D136" s="7"/>
       <c r="E136" s="7"/>
@@ -6179,7 +6179,7 @@
         <v>1</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D137" s="7"/>
       <c r="E137" s="7"/>
@@ -6214,12 +6214,12 @@
         <v>1</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D138" s="7"/>
       <c r="E138" s="7"/>
       <c r="F138" s="7" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="G138" s="3"/>
       <c r="H138" s="3"/>
@@ -6243,18 +6243,18 @@
     </row>
     <row r="139" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
-        <v>271</v>
+        <v>226</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C139" s="7" t="s">
-        <v>224</v>
+      <c r="C139" s="6" t="s">
+        <v>227</v>
       </c>
       <c r="D139" s="7"/>
       <c r="E139" s="7"/>
-      <c r="F139" s="7" t="s">
-        <v>225</v>
+      <c r="F139" s="4" t="s">
+        <v>228</v>
       </c>
       <c r="G139" s="3"/>
       <c r="H139" s="3"/>
@@ -6284,12 +6284,12 @@
         <v>1</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D140" s="7"/>
       <c r="E140" s="7"/>
-      <c r="F140" s="4" t="s">
-        <v>228</v>
+      <c r="F140" s="7" t="s">
+        <v>230</v>
       </c>
       <c r="G140" s="3"/>
       <c r="H140" s="3"/>
@@ -6313,18 +6313,22 @@
     </row>
     <row r="141" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
-        <v>226</v>
+        <v>272</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="D141" s="7"/>
-      <c r="E141" s="7"/>
+        <v>231</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="E141" s="7" t="s">
+        <v>233</v>
+      </c>
       <c r="F141" s="7" t="s">
-        <v>230</v>
+        <v>60</v>
       </c>
       <c r="G141" s="3"/>
       <c r="H141" s="3"/>
@@ -6347,23 +6351,19 @@
       <c r="Y141" s="3"/>
     </row>
     <row r="142" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A142" s="6" t="s">
-        <v>272</v>
+      <c r="A142" s="4" t="s">
+        <v>0</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="D142" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="E142" s="7" t="s">
-        <v>233</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D142" s="7"/>
+      <c r="E142" s="7"/>
       <c r="F142" s="7" t="s">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="G142" s="3"/>
       <c r="H142" s="3"/>
@@ -29120,12 +29120,12 @@
       <c r="Y984" s="3"/>
     </row>
     <row r="985" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A985" s="9"/>
+      <c r="A985" s="3"/>
       <c r="B985" s="3"/>
-      <c r="C985" s="9"/>
-      <c r="D985" s="9"/>
-      <c r="E985" s="9"/>
-      <c r="F985" s="9"/>
+      <c r="C985" s="3"/>
+      <c r="D985" s="3"/>
+      <c r="E985" s="3"/>
+      <c r="F985" s="3"/>
       <c r="G985" s="3"/>
       <c r="H985" s="3"/>
       <c r="I985" s="3"/>
@@ -29281,34 +29281,8 @@
       <c r="X990" s="3"/>
       <c r="Y990" s="3"/>
     </row>
-    <row r="991" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A991" s="3"/>
-      <c r="B991" s="3"/>
-      <c r="C991" s="3"/>
-      <c r="D991" s="3"/>
-      <c r="E991" s="3"/>
-      <c r="F991" s="3"/>
-      <c r="G991" s="3"/>
-      <c r="H991" s="3"/>
-      <c r="I991" s="3"/>
-      <c r="J991" s="3"/>
-      <c r="K991" s="3"/>
-      <c r="L991" s="3"/>
-      <c r="M991" s="3"/>
-      <c r="N991" s="3"/>
-      <c r="O991" s="3"/>
-      <c r="P991" s="3"/>
-      <c r="Q991" s="3"/>
-      <c r="R991" s="3"/>
-      <c r="S991" s="3"/>
-      <c r="T991" s="3"/>
-      <c r="U991" s="3"/>
-      <c r="V991" s="3"/>
-      <c r="W991" s="3"/>
-      <c r="X991" s="3"/>
-      <c r="Y991" s="3"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/wireless-technologies/antennas-and-adapters.xlsx
+++ b/data/wireless-technologies/antennas-and-adapters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\react\dielcom\dielcom\data\wireless-technologies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA09096-765F-4DBD-88C0-D1EDC600E11D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F43C2E-6D7A-49E6-A7AC-7391BD58AE49}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="25065" windowHeight="12675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1208,7 +1208,7 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>235</v>
@@ -1217,7 +1217,7 @@
         <v>276</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>239</v>
@@ -1228,7 +1228,6 @@
       <c r="G1" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
@@ -1250,7 +1249,7 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>240</v>
+        <v>13</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -1259,7 +1258,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>13</v>
+        <v>240</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>6</v>
@@ -1270,7 +1269,6 @@
       <c r="G2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -1292,7 +1290,7 @@
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>240</v>
+        <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>1</v>
@@ -1301,7 +1299,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>7</v>
+        <v>240</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>6</v>
@@ -1310,7 +1308,6 @@
       <c r="G3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
@@ -1332,7 +1329,7 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>240</v>
+        <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>1</v>
@@ -1341,7 +1338,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>9</v>
+        <v>240</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>6</v>
@@ -1350,7 +1347,6 @@
       <c r="G4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -1372,7 +1368,7 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>1</v>
@@ -1381,7 +1377,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>10</v>
+        <v>240</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>6</v>
@@ -1392,7 +1388,6 @@
       <c r="G5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -1414,7 +1409,7 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>240</v>
+        <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>1</v>
@@ -1423,14 +1418,13 @@
         <v>5</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>4</v>
+        <v>240</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>6</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
-      <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -1452,7 +1446,7 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>240</v>
+        <v>16</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>1</v>
@@ -1461,7 +1455,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>16</v>
+        <v>240</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>6</v>
@@ -1472,7 +1466,6 @@
       <c r="G7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -1494,7 +1487,7 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>240</v>
+        <v>17</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>1</v>
@@ -1503,7 +1496,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>17</v>
+        <v>240</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>6</v>
@@ -1514,7 +1507,6 @@
       <c r="G8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -1536,7 +1528,7 @@
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>240</v>
+        <v>18</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>1</v>
@@ -1545,7 +1537,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>6</v>
@@ -1554,7 +1546,6 @@
       <c r="G9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -1576,7 +1567,7 @@
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>240</v>
+        <v>20</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>1</v>
@@ -1585,7 +1576,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>20</v>
+        <v>240</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>6</v>
@@ -1594,7 +1585,6 @@
       <c r="G10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -1616,7 +1606,7 @@
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>240</v>
+        <v>22</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>1</v>
@@ -1625,7 +1615,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>22</v>
+        <v>240</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>6</v>
@@ -1636,7 +1626,6 @@
       <c r="G11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -1658,7 +1647,7 @@
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>240</v>
+        <v>24</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>1</v>
@@ -1667,7 +1656,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>24</v>
+        <v>240</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>6</v>
@@ -1678,7 +1667,6 @@
       <c r="G12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -1700,7 +1688,7 @@
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>240</v>
+        <v>25</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>1</v>
@@ -1709,7 +1697,7 @@
         <v>12</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>25</v>
+        <v>240</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>6</v>
@@ -1718,7 +1706,6 @@
         <v>26</v>
       </c>
       <c r="G13" s="7"/>
-      <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -1740,7 +1727,7 @@
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>240</v>
+        <v>27</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>1</v>
@@ -1749,7 +1736,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>27</v>
+        <v>240</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>6</v>
@@ -1760,7 +1747,6 @@
       <c r="G14" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -1782,7 +1768,7 @@
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>241</v>
+        <v>30</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>1</v>
@@ -1791,7 +1777,7 @@
         <v>14</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>30</v>
+        <v>241</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>6</v>
@@ -1802,7 +1788,6 @@
       <c r="G15" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -1824,7 +1809,7 @@
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>242</v>
+        <v>32</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>1</v>
@@ -1833,7 +1818,7 @@
         <v>15</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>32</v>
+        <v>242</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>6</v>
@@ -1842,7 +1827,6 @@
       <c r="G16" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -1864,7 +1848,7 @@
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>242</v>
+        <v>34</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>1</v>
@@ -1873,7 +1857,7 @@
         <v>16</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>34</v>
+        <v>242</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>6</v>
@@ -1882,7 +1866,6 @@
       <c r="G17" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
@@ -1904,7 +1887,7 @@
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>242</v>
+        <v>35</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>1</v>
@@ -1913,7 +1896,7 @@
         <v>17</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>35</v>
+        <v>242</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>6</v>
@@ -1922,7 +1905,6 @@
       <c r="G18" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
@@ -1944,7 +1926,7 @@
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>1</v>
@@ -1953,7 +1935,7 @@
         <v>18</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>6</v>
@@ -1964,7 +1946,6 @@
       <c r="G19" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
@@ -1986,7 +1967,7 @@
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>243</v>
+        <v>38</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>1</v>
@@ -1995,7 +1976,7 @@
         <v>19</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>38</v>
+        <v>243</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>39</v>
@@ -2004,7 +1985,6 @@
       <c r="G20" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
@@ -2026,7 +2006,7 @@
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>274</v>
+        <v>41</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>1</v>
@@ -2035,7 +2015,7 @@
         <v>20</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>41</v>
+        <v>274</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>42</v>
@@ -2044,7 +2024,6 @@
       <c r="G21" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
@@ -2066,7 +2045,7 @@
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>274</v>
+        <v>44</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>1</v>
@@ -2075,7 +2054,7 @@
         <v>21</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>44</v>
+        <v>274</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>42</v>
@@ -2084,7 +2063,6 @@
       <c r="G22" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
@@ -2106,7 +2084,7 @@
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>274</v>
+        <v>45</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>1</v>
@@ -2115,7 +2093,7 @@
         <v>22</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>45</v>
+        <v>274</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>42</v>
@@ -2126,7 +2104,6 @@
       <c r="G23" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
@@ -2148,7 +2125,7 @@
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>274</v>
+        <v>48</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>1</v>
@@ -2157,7 +2134,7 @@
         <v>23</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>48</v>
+        <v>274</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>42</v>
@@ -2166,7 +2143,6 @@
       <c r="G24" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
@@ -2188,7 +2164,7 @@
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>274</v>
+        <v>50</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>1</v>
@@ -2197,7 +2173,7 @@
         <v>24</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>50</v>
+        <v>274</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>42</v>
@@ -2208,7 +2184,6 @@
       <c r="G25" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
@@ -2230,7 +2205,7 @@
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>244</v>
+        <v>51</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>1</v>
@@ -2239,14 +2214,13 @@
         <v>25</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>51</v>
+        <v>244</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>42</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
-      <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
@@ -2268,7 +2242,7 @@
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>273</v>
+        <v>45</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>1</v>
@@ -2277,7 +2251,7 @@
         <v>26</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>45</v>
+        <v>273</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>52</v>
@@ -2286,7 +2260,6 @@
       <c r="G27" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
@@ -2308,7 +2281,7 @@
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>245</v>
+        <v>53</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>1</v>
@@ -2317,7 +2290,7 @@
         <v>27</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>53</v>
+        <v>245</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>52</v>
@@ -2326,7 +2299,6 @@
       <c r="G28" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
@@ -2348,7 +2320,7 @@
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>245</v>
+        <v>54</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>1</v>
@@ -2357,14 +2329,13 @@
         <v>28</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>54</v>
+        <v>245</v>
       </c>
       <c r="E29" s="8" t="s">
         <v>52</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
-      <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
@@ -2386,7 +2357,7 @@
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>245</v>
+        <v>55</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>1</v>
@@ -2395,14 +2366,13 @@
         <v>29</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>52</v>
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
-      <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
@@ -2424,7 +2394,7 @@
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>275</v>
+        <v>56</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>1</v>
@@ -2433,7 +2403,7 @@
         <v>30</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>56</v>
+        <v>275</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>57</v>
@@ -2444,7 +2414,6 @@
       <c r="G31" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
@@ -2465,8 +2434,8 @@
       <c r="Z31" s="3"/>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>73</v>
+      <c r="A32" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>1</v>
@@ -2474,15 +2443,14 @@
       <c r="C32" s="5">
         <v>31</v>
       </c>
-      <c r="D32" s="7" t="s">
-        <v>59</v>
+      <c r="D32" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
@@ -2503,8 +2471,8 @@
       <c r="Z32" s="3"/>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
-        <v>73</v>
+      <c r="A33" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>1</v>
@@ -2512,15 +2480,14 @@
       <c r="C33" s="5">
         <v>32</v>
       </c>
-      <c r="D33" s="7" t="s">
-        <v>61</v>
+      <c r="D33" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
@@ -2542,7 +2509,7 @@
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>1</v>
@@ -2551,14 +2518,13 @@
         <v>33</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
       <c r="G34" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
@@ -2579,8 +2545,8 @@
       <c r="Z34" s="3"/>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
-        <v>73</v>
+      <c r="A35" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>1</v>
@@ -2588,15 +2554,14 @@
       <c r="C35" s="5">
         <v>34</v>
       </c>
-      <c r="D35" s="7" t="s">
-        <v>63</v>
+      <c r="D35" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
@@ -2617,8 +2582,8 @@
       <c r="Z35" s="3"/>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
-        <v>73</v>
+      <c r="A36" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>1</v>
@@ -2626,15 +2591,14 @@
       <c r="C36" s="5">
         <v>35</v>
       </c>
-      <c r="D36" s="7" t="s">
-        <v>64</v>
+      <c r="D36" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
@@ -2655,8 +2619,8 @@
       <c r="Z36" s="3"/>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
-        <v>73</v>
+      <c r="A37" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>1</v>
@@ -2664,15 +2628,14 @@
       <c r="C37" s="5">
         <v>36</v>
       </c>
-      <c r="D37" s="7" t="s">
-        <v>65</v>
+      <c r="D37" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
@@ -2693,8 +2656,8 @@
       <c r="Z37" s="3"/>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
-        <v>73</v>
+      <c r="A38" s="7" t="s">
+        <v>66</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>1</v>
@@ -2702,15 +2665,14 @@
       <c r="C38" s="5">
         <v>37</v>
       </c>
-      <c r="D38" s="7" t="s">
-        <v>66</v>
+      <c r="D38" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
@@ -2731,8 +2693,8 @@
       <c r="Z38" s="3"/>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
-        <v>73</v>
+      <c r="A39" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>1</v>
@@ -2740,15 +2702,14 @@
       <c r="C39" s="5">
         <v>38</v>
       </c>
-      <c r="D39" s="7" t="s">
-        <v>67</v>
+      <c r="D39" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
@@ -2769,8 +2730,8 @@
       <c r="Z39" s="3"/>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
-        <v>73</v>
+      <c r="A40" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>1</v>
@@ -2778,15 +2739,14 @@
       <c r="C40" s="5">
         <v>39</v>
       </c>
-      <c r="D40" s="7" t="s">
-        <v>68</v>
+      <c r="D40" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
@@ -2807,8 +2767,8 @@
       <c r="Z40" s="3"/>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
-        <v>73</v>
+      <c r="A41" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>1</v>
@@ -2816,15 +2776,14 @@
       <c r="C41" s="5">
         <v>40</v>
       </c>
-      <c r="D41" s="7" t="s">
-        <v>70</v>
+      <c r="D41" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
@@ -2845,8 +2804,8 @@
       <c r="Z41" s="3"/>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
-        <v>73</v>
+      <c r="A42" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>1</v>
@@ -2854,15 +2813,14 @@
       <c r="C42" s="5">
         <v>41</v>
       </c>
-      <c r="D42" s="7" t="s">
-        <v>72</v>
+      <c r="D42" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
@@ -2883,8 +2841,8 @@
       <c r="Z42" s="3"/>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A43" s="6" t="s">
-        <v>73</v>
+      <c r="A43" s="7" t="s">
+        <v>75</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>1</v>
@@ -2892,15 +2850,14 @@
       <c r="C43" s="5">
         <v>42</v>
       </c>
-      <c r="D43" s="7" t="s">
-        <v>75</v>
+      <c r="D43" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
@@ -2921,8 +2878,8 @@
       <c r="Z43" s="3"/>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
-        <v>73</v>
+      <c r="A44" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>1</v>
@@ -2930,15 +2887,14 @@
       <c r="C44" s="5">
         <v>43</v>
       </c>
-      <c r="D44" s="7" t="s">
-        <v>76</v>
+      <c r="D44" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
@@ -2959,8 +2915,8 @@
       <c r="Z44" s="3"/>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
-        <v>73</v>
+      <c r="A45" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>1</v>
@@ -2968,13 +2924,12 @@
       <c r="C45" s="5">
         <v>44</v>
       </c>
-      <c r="D45" s="7" t="s">
-        <v>77</v>
+      <c r="D45" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
-      <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
@@ -2995,8 +2950,8 @@
       <c r="Z45" s="3"/>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
-        <v>246</v>
+      <c r="A46" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>1</v>
@@ -3004,15 +2959,14 @@
       <c r="C46" s="5">
         <v>45</v>
       </c>
-      <c r="D46" s="7" t="s">
-        <v>78</v>
+      <c r="D46" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
@@ -3033,8 +2987,8 @@
       <c r="Z46" s="3"/>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
-        <v>246</v>
+      <c r="A47" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>1</v>
@@ -3042,15 +2996,14 @@
       <c r="C47" s="5">
         <v>46</v>
       </c>
-      <c r="D47" s="7" t="s">
-        <v>79</v>
+      <c r="D47" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
@@ -3071,8 +3024,8 @@
       <c r="Z47" s="3"/>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
-        <v>246</v>
+      <c r="A48" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>1</v>
@@ -3080,15 +3033,14 @@
       <c r="C48" s="5">
         <v>47</v>
       </c>
-      <c r="D48" s="7" t="s">
-        <v>81</v>
+      <c r="D48" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
@@ -3109,8 +3061,8 @@
       <c r="Z48" s="3"/>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
-        <v>246</v>
+      <c r="A49" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>1</v>
@@ -3118,15 +3070,14 @@
       <c r="C49" s="5">
         <v>48</v>
       </c>
-      <c r="D49" s="7" t="s">
-        <v>83</v>
+      <c r="D49" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
       <c r="G49" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
@@ -3148,7 +3099,7 @@
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>247</v>
+        <v>85</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>1</v>
@@ -3157,7 +3108,7 @@
         <v>49</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>85</v>
+        <v>247</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>86</v>
@@ -3168,7 +3119,6 @@
       <c r="G50" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
@@ -3190,7 +3140,7 @@
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>247</v>
+        <v>87</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>1</v>
@@ -3199,7 +3149,7 @@
         <v>50</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>87</v>
+        <v>247</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>86</v>
@@ -3210,7 +3160,6 @@
       <c r="G51" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
@@ -3232,7 +3181,7 @@
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>1</v>
@@ -3241,7 +3190,7 @@
         <v>51</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E52" s="8" t="s">
         <v>91</v>
@@ -3250,7 +3199,6 @@
       <c r="G52" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
@@ -3271,8 +3219,8 @@
       <c r="Z52" s="3"/>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
-        <v>248</v>
+      <c r="A53" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>1</v>
@@ -3280,13 +3228,12 @@
       <c r="C53" s="5">
         <v>52</v>
       </c>
-      <c r="D53" s="7" t="s">
-        <v>93</v>
+      <c r="D53" s="6" t="s">
+        <v>248</v>
       </c>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
-      <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
@@ -3308,7 +3255,7 @@
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>249</v>
+        <v>94</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>1</v>
@@ -3317,7 +3264,7 @@
         <v>53</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>94</v>
+        <v>249</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>95</v>
@@ -3326,7 +3273,6 @@
         <v>96</v>
       </c>
       <c r="G54" s="7"/>
-      <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
@@ -3348,7 +3294,7 @@
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>250</v>
+        <v>97</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>1</v>
@@ -3357,14 +3303,13 @@
         <v>54</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>97</v>
+        <v>250</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>98</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
-      <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
@@ -3386,7 +3331,7 @@
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>1</v>
@@ -3395,14 +3340,13 @@
         <v>55</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
       <c r="G56" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
@@ -3423,8 +3367,8 @@
       <c r="Z56" s="3"/>
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
-        <v>251</v>
+      <c r="A57" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>1</v>
@@ -3432,13 +3376,12 @@
       <c r="C57" s="5">
         <v>56</v>
       </c>
-      <c r="D57" s="7" t="s">
-        <v>102</v>
+      <c r="D57" s="6" t="s">
+        <v>251</v>
       </c>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
       <c r="G57" s="7"/>
-      <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
@@ -3460,7 +3403,7 @@
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>1</v>
@@ -3469,14 +3412,13 @@
         <v>57</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E58" s="7"/>
       <c r="F58" s="7"/>
       <c r="G58" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
@@ -3498,7 +3440,7 @@
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>252</v>
+        <v>106</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>1</v>
@@ -3507,7 +3449,7 @@
         <v>58</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>106</v>
+        <v>252</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>107</v>
@@ -3516,7 +3458,6 @@
       <c r="G59" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3"/>
       <c r="K59" s="3"/>
@@ -3538,7 +3479,7 @@
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>1</v>
@@ -3547,14 +3488,13 @@
         <v>59</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
       <c r="G60" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
       <c r="K60" s="3"/>
@@ -3576,7 +3516,7 @@
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>1</v>
@@ -3585,14 +3525,13 @@
         <v>60</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E61" s="7"/>
       <c r="F61" s="7"/>
       <c r="G61" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="H61" s="3"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3"/>
       <c r="K61" s="3"/>
@@ -3614,7 +3553,7 @@
     </row>
     <row r="62" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>1</v>
@@ -3623,14 +3562,13 @@
         <v>61</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E62" s="7"/>
       <c r="F62" s="7"/>
       <c r="G62" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
@@ -3652,7 +3590,7 @@
     </row>
     <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>253</v>
+        <v>100</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>1</v>
@@ -3661,14 +3599,13 @@
         <v>62</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>100</v>
+        <v>253</v>
       </c>
       <c r="E63" s="7"/>
       <c r="F63" s="7"/>
       <c r="G63" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="H63" s="3"/>
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
       <c r="K63" s="3"/>
@@ -3690,7 +3627,7 @@
     </row>
     <row r="64" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>254</v>
+        <v>114</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>1</v>
@@ -3699,7 +3636,7 @@
         <v>63</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>114</v>
+        <v>254</v>
       </c>
       <c r="E64" s="7"/>
       <c r="F64" s="7" t="s">
@@ -3708,7 +3645,6 @@
       <c r="G64" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="H64" s="3"/>
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
@@ -3730,7 +3666,7 @@
     </row>
     <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>255</v>
+        <v>117</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>1</v>
@@ -3739,14 +3675,13 @@
         <v>64</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>117</v>
+        <v>255</v>
       </c>
       <c r="E65" s="7"/>
       <c r="F65" s="7"/>
       <c r="G65" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="H65" s="3"/>
       <c r="I65" s="3"/>
       <c r="J65" s="3"/>
       <c r="K65" s="3"/>
@@ -3768,7 +3703,7 @@
     </row>
     <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>256</v>
+        <v>119</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>1</v>
@@ -3777,7 +3712,7 @@
         <v>65</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>119</v>
+        <v>256</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>120</v>
@@ -3788,7 +3723,6 @@
       <c r="G66" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H66" s="3"/>
       <c r="I66" s="3"/>
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
@@ -3810,7 +3744,7 @@
     </row>
     <row r="67" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>257</v>
+        <v>122</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>1</v>
@@ -3819,14 +3753,13 @@
         <v>66</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>122</v>
+        <v>257</v>
       </c>
       <c r="E67" s="7"/>
       <c r="F67" s="7"/>
       <c r="G67" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H67" s="3"/>
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
@@ -3848,7 +3781,7 @@
     </row>
     <row r="68" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>258</v>
+        <v>100</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>1</v>
@@ -3857,7 +3790,7 @@
         <v>67</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>100</v>
+        <v>258</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>123</v>
@@ -3866,7 +3799,6 @@
       <c r="G68" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="H68" s="3"/>
       <c r="I68" s="3"/>
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
@@ -3887,8 +3819,8 @@
       <c r="Z68" s="3"/>
     </row>
     <row r="69" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A69" s="6" t="s">
-        <v>259</v>
+      <c r="A69" s="7" t="s">
+        <v>124</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>1</v>
@@ -3896,8 +3828,8 @@
       <c r="C69" s="5">
         <v>68</v>
       </c>
-      <c r="D69" s="7" t="s">
-        <v>124</v>
+      <c r="D69" s="6" t="s">
+        <v>259</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>125</v>
@@ -3908,7 +3840,6 @@
       <c r="G69" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="H69" s="3"/>
       <c r="I69" s="3"/>
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
@@ -3929,8 +3860,8 @@
       <c r="Z69" s="3"/>
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A70" s="6" t="s">
-        <v>259</v>
+      <c r="A70" s="7" t="s">
+        <v>128</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>1</v>
@@ -3938,8 +3869,8 @@
       <c r="C70" s="5">
         <v>69</v>
       </c>
-      <c r="D70" s="7" t="s">
-        <v>128</v>
+      <c r="D70" s="6" t="s">
+        <v>259</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>125</v>
@@ -3950,7 +3881,6 @@
       <c r="G70" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="H70" s="3"/>
       <c r="I70" s="3"/>
       <c r="J70" s="3"/>
       <c r="K70" s="3"/>
@@ -3971,8 +3901,8 @@
       <c r="Z70" s="3"/>
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A71" s="6" t="s">
-        <v>259</v>
+      <c r="A71" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>1</v>
@@ -3980,8 +3910,8 @@
       <c r="C71" s="5">
         <v>70</v>
       </c>
-      <c r="D71" s="7" t="s">
-        <v>129</v>
+      <c r="D71" s="6" t="s">
+        <v>259</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>125</v>
@@ -3992,7 +3922,6 @@
       <c r="G71" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="H71" s="3"/>
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
       <c r="K71" s="3"/>
@@ -4013,8 +3942,8 @@
       <c r="Z71" s="3"/>
     </row>
     <row r="72" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A72" s="6" t="s">
-        <v>259</v>
+      <c r="A72" s="7" t="s">
+        <v>131</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>1</v>
@@ -4022,8 +3951,8 @@
       <c r="C72" s="5">
         <v>71</v>
       </c>
-      <c r="D72" s="7" t="s">
-        <v>131</v>
+      <c r="D72" s="6" t="s">
+        <v>259</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>125</v>
@@ -4034,7 +3963,6 @@
       <c r="G72" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="H72" s="3"/>
       <c r="I72" s="3"/>
       <c r="J72" s="3"/>
       <c r="K72" s="3"/>
@@ -4055,8 +3983,8 @@
       <c r="Z72" s="3"/>
     </row>
     <row r="73" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A73" s="6" t="s">
-        <v>259</v>
+      <c r="A73" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>1</v>
@@ -4064,8 +3992,8 @@
       <c r="C73" s="5">
         <v>72</v>
       </c>
-      <c r="D73" s="7" t="s">
-        <v>132</v>
+      <c r="D73" s="6" t="s">
+        <v>259</v>
       </c>
       <c r="E73" s="7" t="s">
         <v>125</v>
@@ -4076,7 +4004,6 @@
       <c r="G73" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="H73" s="3"/>
       <c r="I73" s="3"/>
       <c r="J73" s="3"/>
       <c r="K73" s="3"/>
@@ -4097,8 +4024,8 @@
       <c r="Z73" s="3"/>
     </row>
     <row r="74" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A74" s="6" t="s">
-        <v>259</v>
+      <c r="A74" s="7" t="s">
+        <v>133</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>1</v>
@@ -4106,8 +4033,8 @@
       <c r="C74" s="5">
         <v>73</v>
       </c>
-      <c r="D74" s="7" t="s">
-        <v>133</v>
+      <c r="D74" s="6" t="s">
+        <v>259</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>125</v>
@@ -4118,7 +4045,6 @@
       <c r="G74" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="H74" s="3"/>
       <c r="I74" s="3"/>
       <c r="J74" s="3"/>
       <c r="K74" s="3"/>
@@ -4140,7 +4066,7 @@
     </row>
     <row r="75" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>260</v>
+        <v>134</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>1</v>
@@ -4149,7 +4075,7 @@
         <v>74</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>134</v>
+        <v>260</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>136</v>
@@ -4160,7 +4086,6 @@
       <c r="G75" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H75" s="3"/>
       <c r="I75" s="3"/>
       <c r="J75" s="3"/>
       <c r="K75" s="3"/>
@@ -4182,7 +4107,7 @@
     </row>
     <row r="76" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>260</v>
+        <v>137</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>1</v>
@@ -4191,7 +4116,7 @@
         <v>75</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>137</v>
+        <v>260</v>
       </c>
       <c r="E76" s="8" t="s">
         <v>136</v>
@@ -4202,7 +4127,6 @@
       <c r="G76" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H76" s="3"/>
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
       <c r="K76" s="3"/>
@@ -4224,7 +4148,7 @@
     </row>
     <row r="77" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>260</v>
+        <v>138</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>1</v>
@@ -4233,7 +4157,7 @@
         <v>76</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>138</v>
+        <v>260</v>
       </c>
       <c r="E77" s="8" t="s">
         <v>136</v>
@@ -4244,7 +4168,6 @@
       <c r="G77" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H77" s="3"/>
       <c r="I77" s="3"/>
       <c r="J77" s="3"/>
       <c r="K77" s="3"/>
@@ -4266,7 +4189,7 @@
     </row>
     <row r="78" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>260</v>
+        <v>139</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>1</v>
@@ -4275,7 +4198,7 @@
         <v>77</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>139</v>
+        <v>260</v>
       </c>
       <c r="E78" s="8" t="s">
         <v>136</v>
@@ -4286,7 +4209,6 @@
       <c r="G78" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H78" s="3"/>
       <c r="I78" s="3"/>
       <c r="J78" s="3"/>
       <c r="K78" s="3"/>
@@ -4308,7 +4230,7 @@
     </row>
     <row r="79" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>260</v>
+        <v>140</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>1</v>
@@ -4317,7 +4239,7 @@
         <v>78</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="E79" s="8" t="s">
         <v>136</v>
@@ -4328,7 +4250,6 @@
       <c r="G79" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H79" s="3"/>
       <c r="I79" s="3"/>
       <c r="J79" s="3"/>
       <c r="K79" s="3"/>
@@ -4350,7 +4271,7 @@
     </row>
     <row r="80" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>260</v>
+        <v>141</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>1</v>
@@ -4359,7 +4280,7 @@
         <v>79</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>141</v>
+        <v>260</v>
       </c>
       <c r="E80" s="8" t="s">
         <v>136</v>
@@ -4370,7 +4291,6 @@
       <c r="G80" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H80" s="3"/>
       <c r="I80" s="3"/>
       <c r="J80" s="3"/>
       <c r="K80" s="3"/>
@@ -4391,8 +4311,8 @@
       <c r="Z80" s="3"/>
     </row>
     <row r="81" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
-        <v>260</v>
+      <c r="A81" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>1</v>
@@ -4400,8 +4320,8 @@
       <c r="C81" s="5">
         <v>80</v>
       </c>
-      <c r="D81" s="6" t="s">
-        <v>142</v>
+      <c r="D81" s="7" t="s">
+        <v>260</v>
       </c>
       <c r="E81" s="8" t="s">
         <v>136</v>
@@ -4410,7 +4330,6 @@
       <c r="G81" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H81" s="3"/>
       <c r="I81" s="3"/>
       <c r="J81" s="3"/>
       <c r="K81" s="3"/>
@@ -4431,8 +4350,8 @@
       <c r="Z81" s="3"/>
     </row>
     <row r="82" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A82" s="7" t="s">
-        <v>260</v>
+      <c r="A82" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>1</v>
@@ -4440,8 +4359,8 @@
       <c r="C82" s="5">
         <v>81</v>
       </c>
-      <c r="D82" s="6" t="s">
-        <v>143</v>
+      <c r="D82" s="7" t="s">
+        <v>260</v>
       </c>
       <c r="E82" s="8" t="s">
         <v>136</v>
@@ -4450,7 +4369,6 @@
       <c r="G82" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H82" s="3"/>
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
@@ -4471,8 +4389,8 @@
       <c r="Z82" s="3"/>
     </row>
     <row r="83" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A83" s="7" t="s">
-        <v>260</v>
+      <c r="A83" s="6" t="s">
+        <v>144</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>1</v>
@@ -4480,8 +4398,8 @@
       <c r="C83" s="5">
         <v>82</v>
       </c>
-      <c r="D83" s="6" t="s">
-        <v>144</v>
+      <c r="D83" s="7" t="s">
+        <v>260</v>
       </c>
       <c r="E83" s="8" t="s">
         <v>136</v>
@@ -4490,7 +4408,6 @@
       <c r="G83" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H83" s="3"/>
       <c r="I83" s="3"/>
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
@@ -4511,8 +4428,8 @@
       <c r="Z83" s="3"/>
     </row>
     <row r="84" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A84" s="7" t="s">
-        <v>260</v>
+      <c r="A84" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>1</v>
@@ -4520,8 +4437,8 @@
       <c r="C84" s="5">
         <v>83</v>
       </c>
-      <c r="D84" s="6" t="s">
-        <v>145</v>
+      <c r="D84" s="7" t="s">
+        <v>260</v>
       </c>
       <c r="E84" s="8" t="s">
         <v>136</v>
@@ -4530,7 +4447,6 @@
       <c r="G84" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H84" s="3"/>
       <c r="I84" s="3"/>
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
@@ -4551,8 +4467,8 @@
       <c r="Z84" s="3"/>
     </row>
     <row r="85" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A85" s="7" t="s">
-        <v>260</v>
+      <c r="A85" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>1</v>
@@ -4560,8 +4476,8 @@
       <c r="C85" s="5">
         <v>84</v>
       </c>
-      <c r="D85" s="6" t="s">
-        <v>146</v>
+      <c r="D85" s="7" t="s">
+        <v>260</v>
       </c>
       <c r="E85" s="8" t="s">
         <v>136</v>
@@ -4570,7 +4486,6 @@
       <c r="G85" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H85" s="3"/>
       <c r="I85" s="3"/>
       <c r="J85" s="3"/>
       <c r="K85" s="3"/>
@@ -4591,8 +4506,8 @@
       <c r="Z85" s="3"/>
     </row>
     <row r="86" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A86" s="7" t="s">
-        <v>260</v>
+      <c r="A86" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>1</v>
@@ -4600,8 +4515,8 @@
       <c r="C86" s="5">
         <v>85</v>
       </c>
-      <c r="D86" s="6" t="s">
-        <v>147</v>
+      <c r="D86" s="7" t="s">
+        <v>260</v>
       </c>
       <c r="E86" s="8" t="s">
         <v>136</v>
@@ -4610,7 +4525,6 @@
       <c r="G86" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H86" s="3"/>
       <c r="I86" s="3"/>
       <c r="J86" s="3"/>
       <c r="K86" s="3"/>
@@ -4632,7 +4546,7 @@
     </row>
     <row r="87" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>260</v>
+        <v>148</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>1</v>
@@ -4641,7 +4555,7 @@
         <v>86</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>148</v>
+        <v>260</v>
       </c>
       <c r="E87" s="8" t="s">
         <v>136</v>
@@ -4650,7 +4564,6 @@
       <c r="G87" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H87" s="3"/>
       <c r="I87" s="3"/>
       <c r="J87" s="3"/>
       <c r="K87" s="3"/>
@@ -4672,7 +4585,7 @@
     </row>
     <row r="88" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>260</v>
+        <v>149</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>1</v>
@@ -4681,7 +4594,7 @@
         <v>87</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>149</v>
+        <v>260</v>
       </c>
       <c r="E88" s="8" t="s">
         <v>136</v>
@@ -4690,7 +4603,6 @@
       <c r="G88" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H88" s="3"/>
       <c r="I88" s="3"/>
       <c r="J88" s="3"/>
       <c r="K88" s="3"/>
@@ -4712,7 +4624,7 @@
     </row>
     <row r="89" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>261</v>
+        <v>150</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>1</v>
@@ -4721,7 +4633,7 @@
         <v>88</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>150</v>
+        <v>261</v>
       </c>
       <c r="E89" s="8" t="s">
         <v>151</v>
@@ -4730,7 +4642,6 @@
       <c r="G89" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="H89" s="3"/>
       <c r="I89" s="3"/>
       <c r="J89" s="3"/>
       <c r="K89" s="3"/>
@@ -4752,7 +4663,7 @@
     </row>
     <row r="90" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>261</v>
+        <v>152</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>1</v>
@@ -4761,7 +4672,7 @@
         <v>89</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>152</v>
+        <v>261</v>
       </c>
       <c r="E90" s="8" t="s">
         <v>151</v>
@@ -4770,7 +4681,6 @@
       <c r="G90" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="H90" s="3"/>
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
@@ -4792,7 +4702,7 @@
     </row>
     <row r="91" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>261</v>
+        <v>153</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>1</v>
@@ -4801,7 +4711,7 @@
         <v>90</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>153</v>
+        <v>261</v>
       </c>
       <c r="E91" s="8" t="s">
         <v>151</v>
@@ -4810,7 +4720,6 @@
       <c r="G91" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="H91" s="3"/>
       <c r="I91" s="3"/>
       <c r="J91" s="3"/>
       <c r="K91" s="3"/>
@@ -4832,7 +4741,7 @@
     </row>
     <row r="92" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>261</v>
+        <v>154</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>1</v>
@@ -4841,7 +4750,7 @@
         <v>91</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>154</v>
+        <v>261</v>
       </c>
       <c r="E92" s="8" t="s">
         <v>151</v>
@@ -4850,7 +4759,6 @@
       <c r="G92" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="H92" s="3"/>
       <c r="I92" s="3"/>
       <c r="J92" s="3"/>
       <c r="K92" s="3"/>
@@ -4872,7 +4780,7 @@
     </row>
     <row r="93" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>262</v>
+        <v>155</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>1</v>
@@ -4881,7 +4789,7 @@
         <v>92</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>155</v>
+        <v>262</v>
       </c>
       <c r="E93" s="8" t="s">
         <v>156</v>
@@ -4890,7 +4798,6 @@
       <c r="G93" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H93" s="3"/>
       <c r="I93" s="3"/>
       <c r="J93" s="3"/>
       <c r="K93" s="3"/>
@@ -4912,7 +4819,7 @@
     </row>
     <row r="94" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>262</v>
+        <v>157</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>1</v>
@@ -4921,7 +4828,7 @@
         <v>93</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>157</v>
+        <v>262</v>
       </c>
       <c r="E94" s="8" t="s">
         <v>156</v>
@@ -4930,7 +4837,6 @@
       <c r="G94" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H94" s="3"/>
       <c r="I94" s="3"/>
       <c r="J94" s="3"/>
       <c r="K94" s="3"/>
@@ -4952,7 +4858,7 @@
     </row>
     <row r="95" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>262</v>
+        <v>158</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>1</v>
@@ -4961,7 +4867,7 @@
         <v>94</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>158</v>
+        <v>262</v>
       </c>
       <c r="E95" s="8" t="s">
         <v>156</v>
@@ -4970,7 +4876,6 @@
       <c r="G95" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H95" s="3"/>
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
@@ -4992,7 +4897,7 @@
     </row>
     <row r="96" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>1</v>
@@ -5001,7 +4906,7 @@
         <v>95</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>159</v>
+        <v>262</v>
       </c>
       <c r="E96" s="8" t="s">
         <v>156</v>
@@ -5010,7 +4915,6 @@
       <c r="G96" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H96" s="3"/>
       <c r="I96" s="3"/>
       <c r="J96" s="3"/>
       <c r="K96" s="3"/>
@@ -5032,7 +4936,7 @@
     </row>
     <row r="97" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
-        <v>262</v>
+        <v>160</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>1</v>
@@ -5041,7 +4945,7 @@
         <v>96</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>160</v>
+        <v>262</v>
       </c>
       <c r="E97" s="8" t="s">
         <v>151</v>
@@ -5050,7 +4954,6 @@
       <c r="G97" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H97" s="3"/>
       <c r="I97" s="3"/>
       <c r="J97" s="3"/>
       <c r="K97" s="3"/>
@@ -5072,7 +4975,7 @@
     </row>
     <row r="98" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>262</v>
+        <v>161</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>1</v>
@@ -5081,7 +4984,7 @@
         <v>97</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>161</v>
+        <v>262</v>
       </c>
       <c r="E98" s="8" t="s">
         <v>151</v>
@@ -5090,7 +4993,6 @@
       <c r="G98" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H98" s="3"/>
       <c r="I98" s="3"/>
       <c r="J98" s="3"/>
       <c r="K98" s="3"/>
@@ -5112,7 +5014,7 @@
     </row>
     <row r="99" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
-        <v>262</v>
+        <v>162</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>1</v>
@@ -5121,7 +5023,7 @@
         <v>98</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>162</v>
+        <v>262</v>
       </c>
       <c r="E99" s="7"/>
       <c r="F99" s="7" t="s">
@@ -5130,7 +5032,6 @@
       <c r="G99" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="H99" s="3"/>
       <c r="I99" s="3"/>
       <c r="J99" s="3"/>
       <c r="K99" s="3"/>
@@ -5152,7 +5053,7 @@
     </row>
     <row r="100" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>262</v>
+        <v>165</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>1</v>
@@ -5161,7 +5062,7 @@
         <v>99</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>165</v>
+        <v>262</v>
       </c>
       <c r="E100" s="7"/>
       <c r="F100" s="7" t="s">
@@ -5170,7 +5071,6 @@
       <c r="G100" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="H100" s="3"/>
       <c r="I100" s="3"/>
       <c r="J100" s="3"/>
       <c r="K100" s="3"/>
@@ -5192,7 +5092,7 @@
     </row>
     <row r="101" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>1</v>
@@ -5201,7 +5101,7 @@
         <v>100</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E101" s="8" t="s">
         <v>156</v>
@@ -5210,7 +5110,6 @@
       <c r="G101" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H101" s="3"/>
       <c r="I101" s="3"/>
       <c r="J101" s="3"/>
       <c r="K101" s="3"/>
@@ -5232,7 +5131,7 @@
     </row>
     <row r="102" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>1</v>
@@ -5241,14 +5140,13 @@
         <v>101</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E102" s="8" t="s">
         <v>91</v>
       </c>
       <c r="F102" s="7"/>
       <c r="G102" s="7"/>
-      <c r="H102" s="3"/>
       <c r="I102" s="3"/>
       <c r="J102" s="3"/>
       <c r="K102" s="3"/>
@@ -5270,7 +5168,7 @@
     </row>
     <row r="103" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>1</v>
@@ -5279,7 +5177,7 @@
         <v>102</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E103" s="8" t="s">
         <v>91</v>
@@ -5288,7 +5186,6 @@
       <c r="G103" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="H103" s="3"/>
       <c r="I103" s="3"/>
       <c r="J103" s="3"/>
       <c r="K103" s="3"/>
@@ -5310,7 +5207,7 @@
     </row>
     <row r="104" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>1</v>
@@ -5319,7 +5216,7 @@
         <v>103</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E104" s="8" t="s">
         <v>91</v>
@@ -5328,7 +5225,6 @@
       <c r="G104" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H104" s="3"/>
       <c r="I104" s="3"/>
       <c r="J104" s="3"/>
       <c r="K104" s="3"/>
@@ -5350,7 +5246,7 @@
     </row>
     <row r="105" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>1</v>
@@ -5359,7 +5255,7 @@
         <v>104</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="E105" s="8" t="s">
         <v>136</v>
@@ -5368,7 +5264,6 @@
       <c r="G105" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H105" s="3"/>
       <c r="I105" s="3"/>
       <c r="J105" s="3"/>
       <c r="K105" s="3"/>
@@ -5390,7 +5285,7 @@
     </row>
     <row r="106" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>263</v>
+        <v>174</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>1</v>
@@ -5399,7 +5294,7 @@
         <v>105</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>174</v>
+        <v>263</v>
       </c>
       <c r="E106" s="8" t="s">
         <v>175</v>
@@ -5410,7 +5305,6 @@
       <c r="G106" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H106" s="3"/>
       <c r="I106" s="3"/>
       <c r="J106" s="3"/>
       <c r="K106" s="3"/>
@@ -5432,7 +5326,7 @@
     </row>
     <row r="107" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
-        <v>264</v>
+        <v>177</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>1</v>
@@ -5441,14 +5335,13 @@
         <v>106</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>177</v>
+        <v>264</v>
       </c>
       <c r="E107" s="7"/>
       <c r="F107" s="7"/>
       <c r="G107" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H107" s="3"/>
       <c r="I107" s="3"/>
       <c r="J107" s="3"/>
       <c r="K107" s="3"/>
@@ -5470,7 +5363,7 @@
     </row>
     <row r="108" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
-        <v>265</v>
+        <v>178</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>1</v>
@@ -5479,7 +5372,7 @@
         <v>107</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>178</v>
+        <v>265</v>
       </c>
       <c r="E108" s="8" t="s">
         <v>179</v>
@@ -5488,7 +5381,6 @@
         <v>163</v>
       </c>
       <c r="G108" s="7"/>
-      <c r="H108" s="3"/>
       <c r="I108" s="3"/>
       <c r="J108" s="3"/>
       <c r="K108" s="3"/>
@@ -5510,7 +5402,7 @@
     </row>
     <row r="109" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
-        <v>266</v>
+        <v>180</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>1</v>
@@ -5519,14 +5411,13 @@
         <v>108</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>180</v>
+        <v>266</v>
       </c>
       <c r="E109" s="8" t="s">
         <v>123</v>
       </c>
       <c r="F109" s="7"/>
       <c r="G109" s="7"/>
-      <c r="H109" s="3"/>
       <c r="I109" s="3"/>
       <c r="J109" s="3"/>
       <c r="K109" s="3"/>
@@ -5547,8 +5438,8 @@
       <c r="Z109" s="3"/>
     </row>
     <row r="110" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A110" s="7" t="s">
-        <v>266</v>
+      <c r="A110" s="6" t="s">
+        <v>181</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>1</v>
@@ -5556,15 +5447,14 @@
       <c r="C110" s="5">
         <v>109</v>
       </c>
-      <c r="D110" s="6" t="s">
-        <v>181</v>
+      <c r="D110" s="7" t="s">
+        <v>266</v>
       </c>
       <c r="E110" s="8" t="s">
         <v>123</v>
       </c>
       <c r="F110" s="7"/>
       <c r="G110" s="7"/>
-      <c r="H110" s="3"/>
       <c r="I110" s="3"/>
       <c r="J110" s="3"/>
       <c r="K110" s="3"/>
@@ -5586,7 +5476,7 @@
     </row>
     <row r="111" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
-        <v>266</v>
+        <v>182</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>1</v>
@@ -5595,7 +5485,7 @@
         <v>110</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>182</v>
+        <v>266</v>
       </c>
       <c r="E111" s="8" t="s">
         <v>123</v>
@@ -5604,7 +5494,6 @@
       <c r="G111" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="H111" s="3"/>
       <c r="I111" s="3"/>
       <c r="J111" s="3"/>
       <c r="K111" s="3"/>
@@ -5625,8 +5514,8 @@
       <c r="Z111" s="3"/>
     </row>
     <row r="112" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A112" s="7" t="s">
-        <v>266</v>
+      <c r="A112" s="6" t="s">
+        <v>184</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>1</v>
@@ -5634,15 +5523,14 @@
       <c r="C112" s="5">
         <v>111</v>
       </c>
-      <c r="D112" s="6" t="s">
-        <v>184</v>
+      <c r="D112" s="7" t="s">
+        <v>266</v>
       </c>
       <c r="E112" s="8" t="s">
         <v>123</v>
       </c>
       <c r="F112" s="7"/>
       <c r="G112" s="7"/>
-      <c r="H112" s="3"/>
       <c r="I112" s="3"/>
       <c r="J112" s="3"/>
       <c r="K112" s="3"/>
@@ -5664,7 +5552,7 @@
     </row>
     <row r="113" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A113" s="6" t="s">
-        <v>267</v>
+        <v>185</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>1</v>
@@ -5673,7 +5561,7 @@
         <v>112</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>185</v>
+        <v>267</v>
       </c>
       <c r="E113" s="6" t="s">
         <v>186</v>
@@ -5684,7 +5572,6 @@
       <c r="G113" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H113" s="3"/>
       <c r="I113" s="3"/>
       <c r="J113" s="3"/>
       <c r="K113" s="3"/>
@@ -5706,7 +5593,7 @@
     </row>
     <row r="114" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
-        <v>267</v>
+        <v>188</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>1</v>
@@ -5715,7 +5602,7 @@
         <v>113</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>188</v>
+        <v>267</v>
       </c>
       <c r="E114" s="4" t="s">
         <v>86</v>
@@ -5726,7 +5613,6 @@
       <c r="G114" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H114" s="3"/>
       <c r="I114" s="3"/>
       <c r="J114" s="3"/>
       <c r="K114" s="3"/>
@@ -5748,7 +5634,7 @@
     </row>
     <row r="115" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A115" s="6" t="s">
-        <v>268</v>
+        <v>174</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>1</v>
@@ -5757,7 +5643,7 @@
         <v>114</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>174</v>
+        <v>268</v>
       </c>
       <c r="E115" s="8" t="s">
         <v>175</v>
@@ -5766,7 +5652,6 @@
       <c r="G115" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="H115" s="3"/>
       <c r="I115" s="3"/>
       <c r="J115" s="3"/>
       <c r="K115" s="3"/>
@@ -5788,7 +5673,7 @@
     </row>
     <row r="116" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>1</v>
@@ -5797,14 +5682,13 @@
         <v>115</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E116" s="7"/>
       <c r="F116" s="7"/>
       <c r="G116" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="H116" s="3"/>
       <c r="I116" s="3"/>
       <c r="J116" s="3"/>
       <c r="K116" s="3"/>
@@ -5826,7 +5710,7 @@
     </row>
     <row r="117" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>1</v>
@@ -5835,14 +5719,13 @@
         <v>116</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E117" s="7"/>
       <c r="F117" s="7"/>
       <c r="G117" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="H117" s="3"/>
       <c r="I117" s="3"/>
       <c r="J117" s="3"/>
       <c r="K117" s="3"/>
@@ -5864,7 +5747,7 @@
     </row>
     <row r="118" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>1</v>
@@ -5873,14 +5756,13 @@
         <v>117</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E118" s="7"/>
       <c r="F118" s="7"/>
       <c r="G118" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="H118" s="3"/>
       <c r="I118" s="3"/>
       <c r="J118" s="3"/>
       <c r="K118" s="3"/>
@@ -5902,7 +5784,7 @@
     </row>
     <row r="119" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A119" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>1</v>
@@ -5911,14 +5793,13 @@
         <v>118</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E119" s="7"/>
       <c r="F119" s="7"/>
       <c r="G119" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="H119" s="3"/>
       <c r="I119" s="3"/>
       <c r="J119" s="3"/>
       <c r="K119" s="3"/>
@@ -5940,7 +5821,7 @@
     </row>
     <row r="120" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>1</v>
@@ -5949,14 +5830,13 @@
         <v>119</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E120" s="7"/>
       <c r="F120" s="7"/>
       <c r="G120" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="H120" s="3"/>
       <c r="I120" s="3"/>
       <c r="J120" s="3"/>
       <c r="K120" s="3"/>
@@ -5978,7 +5858,7 @@
     </row>
     <row r="121" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A121" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>1</v>
@@ -5987,12 +5867,11 @@
         <v>120</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E121" s="7"/>
       <c r="F121" s="7"/>
       <c r="G121" s="7"/>
-      <c r="H121" s="3"/>
       <c r="I121" s="3"/>
       <c r="J121" s="3"/>
       <c r="K121" s="3"/>
@@ -6014,7 +5893,7 @@
     </row>
     <row r="122" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
-        <v>269</v>
+        <v>205</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>1</v>
@@ -6023,14 +5902,13 @@
         <v>121</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>205</v>
+        <v>269</v>
       </c>
       <c r="E122" s="7"/>
       <c r="F122" s="7"/>
       <c r="G122" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="H122" s="3"/>
       <c r="I122" s="3"/>
       <c r="J122" s="3"/>
       <c r="K122" s="3"/>
@@ -6052,7 +5930,7 @@
     </row>
     <row r="123" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A123" s="6" t="s">
-        <v>270</v>
+        <v>206</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>1</v>
@@ -6061,14 +5939,13 @@
         <v>122</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>206</v>
+        <v>270</v>
       </c>
       <c r="E123" s="7"/>
       <c r="F123" s="7"/>
       <c r="G123" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="H123" s="3"/>
       <c r="I123" s="3"/>
       <c r="J123" s="3"/>
       <c r="K123" s="3"/>
@@ -6089,8 +5966,8 @@
       <c r="Z123" s="3"/>
     </row>
     <row r="124" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A124" s="6" t="s">
-        <v>271</v>
+      <c r="A124" s="7" t="s">
+        <v>207</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>1</v>
@@ -6098,15 +5975,14 @@
       <c r="C124" s="5">
         <v>123</v>
       </c>
-      <c r="D124" s="7" t="s">
-        <v>207</v>
+      <c r="D124" s="6" t="s">
+        <v>271</v>
       </c>
       <c r="E124" s="7"/>
       <c r="F124" s="7"/>
       <c r="G124" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="H124" s="3"/>
       <c r="I124" s="3"/>
       <c r="J124" s="3"/>
       <c r="K124" s="3"/>
@@ -6128,7 +6004,7 @@
     </row>
     <row r="125" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A125" s="6" t="s">
-        <v>271</v>
+        <v>209</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>1</v>
@@ -6137,14 +6013,13 @@
         <v>124</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>209</v>
+        <v>271</v>
       </c>
       <c r="E125" s="7"/>
       <c r="F125" s="7"/>
       <c r="G125" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="H125" s="3"/>
       <c r="I125" s="3"/>
       <c r="J125" s="3"/>
       <c r="K125" s="3"/>
@@ -6166,7 +6041,7 @@
     </row>
     <row r="126" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
-        <v>271</v>
+        <v>211</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>1</v>
@@ -6175,14 +6050,13 @@
         <v>125</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>211</v>
+        <v>271</v>
       </c>
       <c r="E126" s="7"/>
       <c r="F126" s="7"/>
       <c r="G126" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="H126" s="3"/>
       <c r="I126" s="3"/>
       <c r="J126" s="3"/>
       <c r="K126" s="3"/>
@@ -6204,7 +6078,7 @@
     </row>
     <row r="127" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
-        <v>271</v>
+        <v>212</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>1</v>
@@ -6213,14 +6087,13 @@
         <v>126</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>212</v>
+        <v>271</v>
       </c>
       <c r="E127" s="7"/>
       <c r="F127" s="7"/>
       <c r="G127" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="H127" s="3"/>
       <c r="I127" s="3"/>
       <c r="J127" s="3"/>
       <c r="K127" s="3"/>
@@ -6242,7 +6115,7 @@
     </row>
     <row r="128" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
-        <v>271</v>
+        <v>214</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>1</v>
@@ -6251,14 +6124,13 @@
         <v>127</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>214</v>
+        <v>271</v>
       </c>
       <c r="E128" s="7"/>
       <c r="F128" s="7"/>
       <c r="G128" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="H128" s="3"/>
       <c r="I128" s="3"/>
       <c r="J128" s="3"/>
       <c r="K128" s="3"/>
@@ -6280,7 +6152,7 @@
     </row>
     <row r="129" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
-        <v>271</v>
+        <v>215</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>1</v>
@@ -6289,14 +6161,13 @@
         <v>128</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>215</v>
+        <v>271</v>
       </c>
       <c r="E129" s="7"/>
       <c r="F129" s="7"/>
       <c r="G129" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="H129" s="3"/>
       <c r="I129" s="3"/>
       <c r="J129" s="3"/>
       <c r="K129" s="3"/>
@@ -6318,7 +6189,7 @@
     </row>
     <row r="130" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
-        <v>271</v>
+        <v>216</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>1</v>
@@ -6327,14 +6198,13 @@
         <v>129</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>216</v>
+        <v>271</v>
       </c>
       <c r="E130" s="7"/>
       <c r="F130" s="7"/>
       <c r="G130" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="H130" s="3"/>
       <c r="I130" s="3"/>
       <c r="J130" s="3"/>
       <c r="K130" s="3"/>
@@ -6356,7 +6226,7 @@
     </row>
     <row r="131" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
-        <v>271</v>
+        <v>217</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>1</v>
@@ -6365,14 +6235,13 @@
         <v>130</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>217</v>
+        <v>271</v>
       </c>
       <c r="E131" s="7"/>
       <c r="F131" s="7"/>
       <c r="G131" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="H131" s="3"/>
       <c r="I131" s="3"/>
       <c r="J131" s="3"/>
       <c r="K131" s="3"/>
@@ -6393,8 +6262,8 @@
       <c r="Z131" s="3"/>
     </row>
     <row r="132" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A132" s="6" t="s">
-        <v>271</v>
+      <c r="A132" s="7" t="s">
+        <v>218</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>1</v>
@@ -6402,15 +6271,14 @@
       <c r="C132" s="5">
         <v>131</v>
       </c>
-      <c r="D132" s="7" t="s">
-        <v>218</v>
+      <c r="D132" s="6" t="s">
+        <v>271</v>
       </c>
       <c r="E132" s="7"/>
       <c r="F132" s="7"/>
       <c r="G132" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="H132" s="3"/>
       <c r="I132" s="3"/>
       <c r="J132" s="3"/>
       <c r="K132" s="3"/>
@@ -6431,8 +6299,8 @@
       <c r="Z132" s="3"/>
     </row>
     <row r="133" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A133" s="6" t="s">
-        <v>271</v>
+      <c r="A133" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>1</v>
@@ -6440,15 +6308,14 @@
       <c r="C133" s="5">
         <v>132</v>
       </c>
-      <c r="D133" s="7" t="s">
-        <v>219</v>
+      <c r="D133" s="6" t="s">
+        <v>271</v>
       </c>
       <c r="E133" s="7"/>
       <c r="F133" s="7"/>
       <c r="G133" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="H133" s="3"/>
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
@@ -6469,8 +6336,8 @@
       <c r="Z133" s="3"/>
     </row>
     <row r="134" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A134" s="6" t="s">
-        <v>271</v>
+      <c r="A134" s="7" t="s">
+        <v>220</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>1</v>
@@ -6478,15 +6345,14 @@
       <c r="C134" s="5">
         <v>133</v>
       </c>
-      <c r="D134" s="7" t="s">
-        <v>220</v>
+      <c r="D134" s="6" t="s">
+        <v>271</v>
       </c>
       <c r="E134" s="7"/>
       <c r="F134" s="7"/>
       <c r="G134" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="H134" s="3"/>
       <c r="I134" s="3"/>
       <c r="J134" s="3"/>
       <c r="K134" s="3"/>
@@ -6507,8 +6373,8 @@
       <c r="Z134" s="3"/>
     </row>
     <row r="135" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A135" s="6" t="s">
-        <v>271</v>
+      <c r="A135" s="7" t="s">
+        <v>221</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>1</v>
@@ -6516,15 +6382,14 @@
       <c r="C135" s="5">
         <v>134</v>
       </c>
-      <c r="D135" s="7" t="s">
-        <v>221</v>
+      <c r="D135" s="6" t="s">
+        <v>271</v>
       </c>
       <c r="E135" s="7"/>
       <c r="F135" s="7"/>
       <c r="G135" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="H135" s="3"/>
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
@@ -6545,8 +6410,8 @@
       <c r="Z135" s="3"/>
     </row>
     <row r="136" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A136" s="6" t="s">
-        <v>271</v>
+      <c r="A136" s="7" t="s">
+        <v>222</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>1</v>
@@ -6554,15 +6419,14 @@
       <c r="C136" s="5">
         <v>135</v>
       </c>
-      <c r="D136" s="7" t="s">
-        <v>222</v>
+      <c r="D136" s="6" t="s">
+        <v>271</v>
       </c>
       <c r="E136" s="7"/>
       <c r="F136" s="7"/>
       <c r="G136" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="H136" s="3"/>
       <c r="I136" s="3"/>
       <c r="J136" s="3"/>
       <c r="K136" s="3"/>
@@ -6583,8 +6447,8 @@
       <c r="Z136" s="3"/>
     </row>
     <row r="137" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A137" s="6" t="s">
-        <v>271</v>
+      <c r="A137" s="7" t="s">
+        <v>223</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>1</v>
@@ -6592,15 +6456,14 @@
       <c r="C137" s="5">
         <v>136</v>
       </c>
-      <c r="D137" s="7" t="s">
-        <v>223</v>
+      <c r="D137" s="6" t="s">
+        <v>271</v>
       </c>
       <c r="E137" s="7"/>
       <c r="F137" s="7"/>
       <c r="G137" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="H137" s="3"/>
       <c r="I137" s="3"/>
       <c r="J137" s="3"/>
       <c r="K137" s="3"/>
@@ -6621,8 +6484,8 @@
       <c r="Z137" s="3"/>
     </row>
     <row r="138" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A138" s="6" t="s">
-        <v>271</v>
+      <c r="A138" s="7" t="s">
+        <v>224</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>1</v>
@@ -6630,15 +6493,14 @@
       <c r="C138" s="5">
         <v>137</v>
       </c>
-      <c r="D138" s="7" t="s">
-        <v>224</v>
+      <c r="D138" s="6" t="s">
+        <v>271</v>
       </c>
       <c r="E138" s="7"/>
       <c r="F138" s="7"/>
       <c r="G138" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="H138" s="3"/>
       <c r="I138" s="3"/>
       <c r="J138" s="3"/>
       <c r="K138" s="3"/>
@@ -6660,7 +6522,7 @@
     </row>
     <row r="139" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>1</v>
@@ -6669,14 +6531,13 @@
         <v>138</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E139" s="7"/>
       <c r="F139" s="7"/>
       <c r="G139" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="H139" s="3"/>
       <c r="I139" s="3"/>
       <c r="J139" s="3"/>
       <c r="K139" s="3"/>
@@ -6698,7 +6559,7 @@
     </row>
     <row r="140" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>1</v>
@@ -6707,14 +6568,13 @@
         <v>139</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E140" s="7"/>
       <c r="F140" s="7"/>
       <c r="G140" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="H140" s="3"/>
       <c r="I140" s="3"/>
       <c r="J140" s="3"/>
       <c r="K140" s="3"/>
@@ -6736,7 +6596,7 @@
     </row>
     <row r="141" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
-        <v>272</v>
+        <v>231</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>1</v>
@@ -6745,7 +6605,7 @@
         <v>140</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c r="E141" s="8" t="s">
         <v>232</v>
@@ -6756,7 +6616,6 @@
       <c r="G141" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="H141" s="3"/>
       <c r="I141" s="3"/>
       <c r="J141" s="3"/>
       <c r="K141" s="3"/>
@@ -6777,8 +6636,8 @@
       <c r="Z141" s="3"/>
     </row>
     <row r="142" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A142" s="4" t="s">
-        <v>0</v>
+      <c r="A142" s="6" t="s">
+        <v>2</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>1</v>
@@ -6786,15 +6645,14 @@
       <c r="C142" s="5">
         <v>141</v>
       </c>
-      <c r="D142" s="6" t="s">
-        <v>2</v>
+      <c r="D142" s="4" t="s">
+        <v>0</v>
       </c>
       <c r="E142" s="7"/>
       <c r="F142" s="7"/>
       <c r="G142" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="H142" s="3"/>
       <c r="I142" s="3"/>
       <c r="J142" s="3"/>
       <c r="K142" s="3"/>
